--- a/AQC Attendee List.xlsx
+++ b/AQC Attendee List.xlsx
@@ -2094,7 +2094,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ns1:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
@@ -2323,7 +2323,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2359,7 +2359,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.499984740745262"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3144,7 +3144,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" ns2:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="7"/>
       <tableStyleElement type="headerRow" dxfId="6"/>
       <tableStyleElement type="totalRow" dxfId="5"/>
@@ -3153,7 +3153,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="2"/>
       <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" ns2:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="17"/>
       <tableStyleElement type="totalRow" dxfId="16"/>
       <tableStyleElement type="firstRowStripe" dxfId="15"/>
@@ -3167,8 +3167,8 @@
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>

--- a/AQC Attendee List.xlsx
+++ b/AQC Attendee List.xlsx
@@ -2094,7 +2094,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ns1:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
@@ -2323,7 +2323,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.499984740745262"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2359,7 +2359,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3144,7 +3144,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" ns2:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="7"/>
       <tableStyleElement type="headerRow" dxfId="6"/>
       <tableStyleElement type="totalRow" dxfId="5"/>
@@ -3153,7 +3153,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="2"/>
       <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" ns2:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="17"/>
       <tableStyleElement type="totalRow" dxfId="16"/>
       <tableStyleElement type="firstRowStripe" dxfId="15"/>
@@ -3167,8 +3167,8 @@
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
